--- a/stories/qualys-ci-lookup-rules/Qualys CI Lookup Rules - Plain English Primer.xlsx
+++ b/stories/qualys-ci-lookup-rules/Qualys CI Lookup Rules - Plain English Primer.xlsx
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1156,7 +1156,143 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Hostname vs domain vs FQDN vs DNS - the same machine, four angles</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Take the real name from the payload: ah-1047132-001.sdi.corp.bankofamerica.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Piece</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Analogy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Hostname</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>ah-1047132-001</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>The machine's own short name. Unique only inside its domain: another ah-1047132-001 can exist in hk.baml.com. No dots.</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>First name</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>sdi.corp.bankofamerica.com</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>The area the name belongs to.</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Surname + address</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>FQDN</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>ah-1047132-001.sdi.corp.bankofamerica.com</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Hostname + domain. "Fully qualified" = nothing missing, so it is unique everywhere. Has dots.</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Full name on an envelope</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>DNS</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>(not a name)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>The phone book of the network: it translates names to IP addresses and back. Qualys asks DNS "who is 171.128.225.96?", DNS answers with the FQDN, and Qualys puts that answer in the payload field it calls DNS. So the DNS field holds an FQDN (occasionally just a hostname, when the phone book only knows the short name).</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>The phone book</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Quick test: no dots = hostname; dots = FQDN; "DNS" = where the FQDN came from. The rules check every way a CI may have stored the name: the FQDN in the fqdn field (250/260), the hostname in name with the domain in dns_domain (300/310), the hostname alone (400/410), the whole FQDN typed into name (450/850).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A26:D26"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/stories/qualys-ci-lookup-rules/Qualys CI Lookup Rules - Plain English Primer.xlsx
+++ b/stories/qualys-ci-lookup-rules/Qualys CI Lookup Rules - Plain English Primer.xlsx
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Discovery sometimes does not write the name on the CI at all; it keeps a separate DNS Name record linked to an IP Address record, linked to a network adapter, linked to the CI. This rule follows that chain from the scanned name. Count the distinct CIs at the end: one -&gt; match; several -&gt; the one reached through the scanned IP. An alias resolves to the real machine because the chain ends on whatever device holds the address.</t>
+          <t>Discovery sometimes does not write the name on the CI at all; it keeps a separate DNS Name record linked to an IP Address record, linked to a network adapter, linked to the CI. This rule follows that chain from the scanned name. A CI at the end of the chain whose class contradicts the OS (a Computer for a Cisco IOS host) is left out. Count the remaining CIs: one -&gt; match; several -&gt; the one reached through the scanned IP. An alias resolves to the real machine because the chain ends on whatever device holds the address.</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>No DNS Name record; the name points to two devices and the IP does not pick one.</t>
+          <t>No DNS Name record; the only CI at the end of the chain is of a class the OS rules out; the name points to two devices and the IP does not pick one.</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Search all hardware for exactly one CI with the hostname. Then a sanity check: if the OS says AIX and the CI found is a Windows Server, that is a namesake, refuse it. A generic class (Server, Computer, UNIX Server) never contradicts.</t>
+          <t>Search all hardware for exactly one CI with the hostname. Then a sanity check: the CI must be of the class the OS implies, a sub-class of it, or a parent of it (a plain Server for an AIX host is fine; a Windows Server or a Computer for a Cisco IOS host is a namesake and is refused).</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Exactly one hardware CI on the address. Refuse it if it is a load balancer (the address is a VIP) or if its class contradicts the OS (generic classes never do).</t>
+          <t>Exactly one hardware CI on the address. Refuse it if it is a load balancer (the address is a VIP) or if its class contradicts the OS (a parent class such as Server or Hardware never does).</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>A server with several network cards keeps its addresses on Network Adapter records, not on the CI. Find adapters carrying the address; count the distinct owning CIs (one server with two cards counts once). One owner, not a balancer -&gt; match.</t>
+          <t>A server with several network cards keeps its addresses on Network Adapter records, not on the CI. Find adapters carrying the address; skip owners whose class contradicts the OS; count the distinct owning CIs (one server with two cards counts once). One owner, not a balancer -&gt; match.</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Newer discovery writes each address as an IP Address record linked to the adapter, and the adapter itself may carry nothing. Read those records: IP Address -&gt; adapter -&gt; CI. Same counting as 730.</t>
+          <t>Newer discovery writes each address as an IP Address record linked to the adapter, and the adapter itself may carry nothing. Read those records: IP Address -&gt; adapter -&gt; CI. Same counting and the same class check as 730.</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -3243,58 +3243,70 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Why is the IP address used last?</t>
+          <t>What does "class contradicts the OS" mean?</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>It is the weakest fact: addresses move between machines and load balancers answer on shared virtual IPs. It is used only when there is no serial and no usable name.</t>
+          <t>The CI found must be of the class the OS implies, a sub-class of it, or a parent of it. Cisco IOS implies Network Gear: an IP Router or a plain Hardware record agrees, a Computer or a Server does not. Every rule that can land outside the OS class applies this check, including the ones that follow discovery records (350, 730, 740).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>What do the three new rules add?</t>
+          <t>Why is the IP address used last?</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>They handle labels that are not a machine's own name: management controllers (server-ilo -&gt; the server), switch interfaces (device-vlan705 -&gt; the switch), and load balancer virtual IPs (-&gt; the Load Balancer Service CI). Together they cover the biggest groups on the unmatched list.</t>
+          <t>It is the weakest fact: addresses move between machines and load balancers answer on shared virtual IPs. It is used only when there is no serial and no usable name.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Where do the suffix and marker lists live?</t>
+          <t>What do the three new rules add?</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>In the rule scripts themselves, as short lists at the top of the relevant stage. No custom system properties.</t>
+          <t>They handle labels that are not a machine's own name: management controllers (server-ilo -&gt; the server), switch interfaces (device-vlan705 -&gt; the switch), and load balancer virtual IPs (-&gt; the Load Balancer Service CI). Together they cover the biggest groups on the unmatched list.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>What happens to a host no rule can place?</t>
+          <t>Where do the suffix and marker lists live?</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>It stays on the Unmatched CI list. Nothing is attached to a wrong CI.</t>
+          <t>In the rule scripts themselves, as short lists at the top of the relevant stage. No custom system properties.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>What happens to a host no rule can place?</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>It stays on the Unmatched CI list. Nothing is attached to a wrong CI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
           <t>How were the rules tested?</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Each rule was run against fixture CIs for its positive case and its decline cases (nothing found, two found, wrong class, load balancer), and a sample of real unmatched payloads was run through the whole chain before and after.</t>
         </is>

--- a/stories/qualys-ci-lookup-rules/Qualys CI Lookup Rules - Plain English Primer.xlsx
+++ b/stories/qualys-ci-lookup-rules/Qualys CI Lookup Rules - Plain English Primer.xlsx
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Narrow first: inside the class the OS points at, where a namesake of another type cannot appear. Wide second: the whole hardware tree, for hosts whose OS is unknown (a third of the feed) or whose CI is stored as a generic Server.</t>
+          <t>Narrow first: inside the class the OS points at, where a namesake of another type cannot appear. Wide second: the whole hardware tree, for hosts whose OS is unknown (a third of the feed) or whose CI is stored as a plain Server. The wide rules, and the rules that follow discovery records, still refuse a CI whose class does not fit the OS: for a Cisco IOS host, Network Gear or Hardware is fine, a Computer is not.</t>
         </is>
       </c>
     </row>
